--- a/data/trans_bre/IP2003-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP2003-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 6,85</t>
+          <t>-9,16; 7,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 21,15</t>
+          <t>2,3; 20,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 10,67</t>
+          <t>-7,92; 11,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 8,3</t>
+          <t>-6,59; 7,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-48,75; 62,75</t>
+          <t>-48,64; 66,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,87; 428,02</t>
+          <t>11,62; 397,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-43,68; 94,37</t>
+          <t>-41,73; 105,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-46,64; 126,79</t>
+          <t>-48,24; 116,22</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 9,15</t>
+          <t>-7,08; 9,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 14,6</t>
+          <t>-2,08; 14,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 9,05</t>
+          <t>-4,88; 8,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 8,61</t>
+          <t>-10,04; 6,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,42; 133,18</t>
+          <t>-51,12; 153,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 222,5</t>
+          <t>-20,43; 215,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,5; 179,09</t>
+          <t>-46,09; 182,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-54,62; 88,51</t>
+          <t>-51,67; 67,05</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 7,76</t>
+          <t>-9,11; 7,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 13,37</t>
+          <t>-5,09; 12,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 9,52</t>
+          <t>-7,91; 9,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 11,84</t>
+          <t>-11,65; 10,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-59,57; 80,62</t>
+          <t>-53,66; 72,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,23; 138,63</t>
+          <t>-29,31; 135,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-68,12; 191,69</t>
+          <t>-63,03; 190,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-63,3; 235,88</t>
+          <t>-65,68; 198,87</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 6,47</t>
+          <t>-5,46; 6,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 7,24</t>
+          <t>-3,4; 8,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 6,49</t>
+          <t>-5,04; 6,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 33,2</t>
+          <t>-6,7; 39,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,6; 56,3</t>
+          <t>-30,53; 56,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,25; 75,73</t>
+          <t>-22,4; 80,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,47; 62,61</t>
+          <t>-30,31; 57,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,98; 273,94</t>
+          <t>-37,42; 300,99</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 16,37</t>
+          <t>-1,04; 16,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 11,06</t>
+          <t>-4,78; 10,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 7,01</t>
+          <t>-6,67; 6,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 15,74</t>
+          <t>-13,19; 15,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 113,02</t>
+          <t>-5,47; 117,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,74; 89,7</t>
+          <t>-23,97; 84,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-40,65; 62,72</t>
+          <t>-36,92; 60,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-48,5; 161,73</t>
+          <t>-52,06; 158,6</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,87; 23,16</t>
+          <t>5,46; 22,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 6,45</t>
+          <t>-14,36; 6,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 15,64</t>
+          <t>-7,08; 15,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 6,8</t>
+          <t>-9,47; 6,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58,84; 1037,72</t>
+          <t>41,65; 942,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,99; 54,44</t>
+          <t>-64,56; 59,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,52; 170,05</t>
+          <t>-38,03; 199,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-75,73; 198,29</t>
+          <t>-77,86; 211,05</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 6,23</t>
+          <t>-0,67; 6,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 7,03</t>
+          <t>0,16; 6,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 4,39</t>
+          <t>-1,9; 4,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 14,95</t>
+          <t>-2,35; 14,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 49,99</t>
+          <t>-4,46; 47,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,77; 60,46</t>
+          <t>1,22; 59,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 38,78</t>
+          <t>-13,3; 36,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 122,98</t>
+          <t>-16,31; 109,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2003-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP2003-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 7,14</t>
+          <t>-9,71; 7,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 20,71</t>
+          <t>2,0; 20,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 11,58</t>
+          <t>-8,61; 10,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 7,84</t>
+          <t>-6,67; 7,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-48,64; 66,12</t>
+          <t>-51,26; 76,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,62; 397,09</t>
+          <t>8,75; 373,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-41,73; 105,32</t>
+          <t>-46,23; 91,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-48,24; 116,22</t>
+          <t>-48,51; 122,22</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 9,67</t>
+          <t>-7,51; 8,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 14,72</t>
+          <t>-1,99; 14,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 8,52</t>
+          <t>-4,67; 9,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 6,83</t>
+          <t>-11,18; 6,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,12; 153,18</t>
+          <t>-52,36; 126,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 215,95</t>
+          <t>-16,3; 223,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,09; 182,46</t>
+          <t>-44,2; 201,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,67; 67,05</t>
+          <t>-56,95; 62,82</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 7,43</t>
+          <t>-8,57; 7,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 12,55</t>
+          <t>-5,12; 13,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 9,86</t>
+          <t>-8,57; 8,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 10,93</t>
+          <t>-10,03; 12,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-53,66; 72,12</t>
+          <t>-49,68; 81,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,31; 135,52</t>
+          <t>-31,18; 132,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-63,03; 190,43</t>
+          <t>-69,15; 164,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-65,68; 198,87</t>
+          <t>-58,59; 219,97</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 6,53</t>
+          <t>-5,69; 6,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 8,11</t>
+          <t>-3,79; 7,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 6,05</t>
+          <t>-5,86; 5,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 39,43</t>
+          <t>-6,25; 36,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,53; 56,43</t>
+          <t>-32,8; 55,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,4; 80,74</t>
+          <t>-26,3; 75,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-30,31; 57,96</t>
+          <t>-35,56; 55,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,42; 300,99</t>
+          <t>-35,79; 292,21</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 16,78</t>
+          <t>-1,33; 16,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 10,26</t>
+          <t>-5,22; 9,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 6,73</t>
+          <t>-6,54; 7,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 15,82</t>
+          <t>-14,25; 15,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 117,78</t>
+          <t>-7,86; 115,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,97; 84,88</t>
+          <t>-26,73; 77,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-36,92; 60,34</t>
+          <t>-35,16; 67,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-52,06; 158,6</t>
+          <t>-51,98; 152,48</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,46; 22,69</t>
+          <t>5,55; 23,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 6,28</t>
+          <t>-14,77; 6,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 15,57</t>
+          <t>-7,97; 14,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 6,58</t>
+          <t>-8,94; 6,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41,65; 942,02</t>
+          <t>40,45; 1029,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,56; 59,09</t>
+          <t>-68,03; 51,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,03; 199,48</t>
+          <t>-43,2; 160,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-77,86; 211,05</t>
+          <t>-70,72; 231,13</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 6,0</t>
+          <t>-0,61; 5,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 6,95</t>
+          <t>0,43; 6,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 4,24</t>
+          <t>-1,86; 4,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 14,26</t>
+          <t>-2,97; 15,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 47,96</t>
+          <t>-4,02; 48,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 59,58</t>
+          <t>2,5; 57,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 36,75</t>
+          <t>-14,19; 38,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 109,79</t>
+          <t>-19,75; 109,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2003-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP2003-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>1,1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 7,6</t>
+          <t>-9,39; 6,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 20,29</t>
+          <t>2,91; 21,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 10,08</t>
+          <t>-7,88; 10,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 7,92</t>
+          <t>-6,86; 8,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-51,26; 76,19</t>
+          <t>-48,75; 62,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,75; 373,31</t>
+          <t>21,87; 428,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-46,23; 91,84</t>
+          <t>-43,68; 94,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-48,51; 122,22</t>
+          <t>-47,22; 123,52</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,4</t>
+          <t>-1,21</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-9,37%</t>
+          <t>-8,25%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 8,69</t>
+          <t>-7,17; 9,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 14,84</t>
+          <t>-1,71; 14,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 9,36</t>
+          <t>-5,31; 9,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 6,89</t>
+          <t>-10,33; 8,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,36; 126,2</t>
+          <t>-50,42; 133,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 223,29</t>
+          <t>-14,97; 222,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,2; 201,55</t>
+          <t>-45,5; 179,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-56,95; 62,82</t>
+          <t>-53,92; 93,88</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 7,88</t>
+          <t>-9,88; 7,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 13,09</t>
+          <t>-5,32; 13,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 8,53</t>
+          <t>-8,35; 9,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 12,1</t>
+          <t>-10,98; 12,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,68; 81,6</t>
+          <t>-59,57; 80,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,18; 132,32</t>
+          <t>-27,23; 138,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-69,15; 164,86</t>
+          <t>-68,12; 191,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-58,59; 219,97</t>
+          <t>-65,82; 239,48</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,93</t>
+          <t>-0,82</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>-4,86%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 6,43</t>
+          <t>-5,46; 6,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 7,4</t>
+          <t>-3,74; 7,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 5,8</t>
+          <t>-4,97; 6,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 36,34</t>
+          <t>-9,34; 7,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,8; 55,08</t>
+          <t>-30,6; 56,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,3; 75,93</t>
+          <t>-27,25; 75,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,56; 55,02</t>
+          <t>-29,47; 62,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,79; 292,21</t>
+          <t>-44,12; 59,04</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,37</t>
+          <t>3,24</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 16,44</t>
+          <t>-2,49; 16,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 9,95</t>
+          <t>-4,73; 11,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 7,56</t>
+          <t>-7,51; 7,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 15,05</t>
+          <t>-12,53; 12,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 115,13</t>
+          <t>-13,29; 113,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 77,99</t>
+          <t>-23,74; 89,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-35,16; 67,11</t>
+          <t>-40,65; 62,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-51,98; 152,48</t>
+          <t>-49,76; 142,54</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-10,03%</t>
+          <t>-6,04%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,55; 23,24</t>
+          <t>5,87; 23,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 6,63</t>
+          <t>-14,32; 6,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 14,5</t>
+          <t>-7,54; 15,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 6,55</t>
+          <t>-8,75; 7,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,45; 1029,28</t>
+          <t>58,84; 1037,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,03; 51,06</t>
+          <t>-65,99; 54,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,2; 160,1</t>
+          <t>-41,52; 170,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,72; 231,13</t>
+          <t>-74,03; 209,15</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,15</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 5,87</t>
+          <t>-0,47; 6,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 6,91</t>
+          <t>0,44; 7,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 4,3</t>
+          <t>-2,27; 4,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 15,24</t>
+          <t>-4,11; 3,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 48,79</t>
+          <t>-3,39; 49,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 57,72</t>
+          <t>1,77; 60,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 38,53</t>
+          <t>-16,13; 38,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-19,75; 109,79</t>
+          <t>-24,92; 33,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2003-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP2003-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,23</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10,91</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,21</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-8,16%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>123,88%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.233351541484923</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>10.90640694864736</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.208907338978685</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.100820260701016</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.08159830125721644</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1.238816975332016</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.07917639765218652</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.1017963418923647</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-9,39; 6,85</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2,91; 21,15</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-7,88; 10,67</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-6,86; 8,69</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-48,75; 62,75</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>21,87; 428,02</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-43,68; 94,37</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-47,22; 123,52</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-9.388480592428012</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>2.910663053387869</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-7.875943984336311</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-6.857139673687734</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.4874769262116401</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>0.2187121482029701</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.4367565646605285</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.4722349224848271</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.845483384025407</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>21.14691979396053</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10.66690549313214</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8.690033625096225</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.6275183815950149</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>4.280211557059255</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.9437260615386792</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.235214739811864</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6,16</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,76</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,21</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,92%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>59,77%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>21,01%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-8,25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-7,17; 9,15</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1,71; 14,6</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,31; 9,05</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-10,33; 8,95</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-50,42; 133,18</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-14,97; 222,5</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-45,5; 179,09</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-53,92; 93,88</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.7488102678512465</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>6.163582344277089</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.762571177196777</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.212293910974499</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.06916461902606003</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.597668675881479</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.2101434816619091</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.08251748407434736</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-1,19</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,64</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-8,37%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>12,78%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-7.170460857857343</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.707013117419213</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.305395242328711</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-10.32815164519411</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5042135108127627</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1497442215003232</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4550125117629733</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.5391548485942949</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-9,88; 7,76</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-5,32; 13,37</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-8,35; 9,52</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-10,98; 12,01</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-59,57; 80,62</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-27,23; 138,63</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-68,12; 191,69</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-65,82; 239,48</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>9.152270285609049</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>14.59690713961307</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>9.048135550088597</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>8.949167328493136</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.331849187585646</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>2.224982738925815</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.790886707799527</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.9388096973164424</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,71</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,11</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,82</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,37%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-4,86%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-1.189069529941073</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.639934919156099</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1837167415519522</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.40107075269881</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.08370695981031825</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.2571340427932463</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.01981135655486004</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.1277559705576189</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-5,46; 6,47</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,74; 7,24</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,97; 6,49</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-9,34; 7,43</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-30,6; 56,3</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-27,25; 75,73</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-29,47; 62,61</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-44,12; 59,04</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-9.880045830571733</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.323734907175382</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-8.34685241013787</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-10.98204812294038</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5957011318291495</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.2722798805383882</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.6812250807236708</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.6581889913176474</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7.757949564192089</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>13.37396015830779</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.515157088872204</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>12.00978700432224</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.8062238561101976</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.386327554125714</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.916905280862683</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>2.394777237372424</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>7,51</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,82</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,24</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>42,53%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>17,21%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>20,45%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,49; 16,37</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-4,73; 11,06</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-7,51; 7,01</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-12,53; 12,62</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-13,29; 113,02</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-23,74; 89,7</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-40,65; 62,72</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-49,76; 142,54</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>0.7062949937062329</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2.10945064760844</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.7374081782370923</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.8185806134206025</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.04883351049256808</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.1736814155531899</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.05481595431345186</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.0485859212502399</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>14,5</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-3,73</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3,34</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>287,01%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-21,97%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>23,74%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-6,04%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-5.463609465382854</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.735961703998915</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-4.967354418197935</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-9.336929833210775</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3060367142754847</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2724935482312117</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.2946774015903761</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.4412372899508455</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>5,87; 23,16</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-14,32; 6,45</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-7,54; 15,64</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-8,75; 7,16</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>58,84; 1037,72</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-65,99; 54,44</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-41,52; 170,05</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-74,03; 209,15</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6.466809817019239</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7.239844435750009</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.486130634606674</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>7.425232753273734</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.5630254156469526</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.7573109890877021</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.6261426854985497</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.590393124658999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>2,72</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3,69</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,08</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>19,86%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28,24%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,46%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>7.514634952580498</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2.820807067954634</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.2206668165280729</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>3.240272297732902</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.4252796941522122</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.1720680392592278</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.01484457921351198</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.204510810307322</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,47; 6,23</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0,44; 7,03</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-2,27; 4,39</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-4,11; 3,95</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-3,39; 49,99</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,77; 60,46</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-16,13; 38,78</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-24,92; 33,33</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.489590296138105</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-4.727094314629611</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-7.506931936249616</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-12.5321487679816</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.132890489020833</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2373840010181789</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.4065336656186684</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.4976104072409097</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>16.37304901177976</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>11.06199456962165</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>7.011934604083084</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>12.61601289018789</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.130243633650358</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.8969718909846562</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.6272137293825586</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>1.425420070722127</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>14.49627799229458</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-3.732253745957434</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>3.335706829205484</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-0.4549213452601106</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>2.870088466945307</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.2197228126250677</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.2374200804004752</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.06039491084963457</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>5.873910107654166</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-14.32253801889045</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-7.537047985722325</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-8.748228816268172</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0.5884482427258065</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.6599172516857477</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.4151744868297125</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.7402974164908788</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>23.15892938910423</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>6.453286814021351</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>15.64226732808091</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>7.158679719510154</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>10.37715979194515</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.5444476068120828</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>1.70053551245235</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>2.091491346808103</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>2.721657857853574</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3.688061059959524</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1.08327993251498</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.3398843561262882</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.1986392801819787</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.2823590080469386</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.08463200742095423</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.0245377369361536</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.4734961279365771</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0.4429819679822782</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-2.270267430758495</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-4.112186551335284</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.03392379219916575</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>0.01769126500290936</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.161328372522463</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.2491587517679321</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>6.226557988490644</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>7.028736515753324</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>4.393062175425786</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>3.946787920267338</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.4999355136635456</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.6046071707849224</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.3877843523562667</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.3332940077438695</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
